--- a/propuesta-bootcamp-ejecutivo-quito-2026/outputs/export/comparativa-productos.xlsx
+++ b/propuesta-bootcamp-ejecutivo-quito-2026/outputs/export/comparativa-productos.xlsx
@@ -48,7 +48,7 @@
     <t>Directivos y managers</t>
   </si>
   <si>
-    <t>Agente funcional con contexto real</t>
+    <t>Agente funcional con contexto real (operativo para tareas basicas desde el dia 1)</t>
   </si>
   <si>
     <t>CAO Bootcamp - Edicion Creyentes</t>
@@ -66,7 +66,7 @@
     <t>Directivos C-level, fundadores</t>
   </si>
   <si>
-    <t>1 agente propio (Instalamos a Pristino, agente Open Source desarrollado y mantenido por MetodologIA, obra de Javier Montano. Suyo para siempre, auditable, corre en local)</t>
+    <t>1 agente propio (Instalamos a Pristino, agente Open Source de Javier Montano. En el taller aprende a usarlo en su version basica. Sacarle todo el potencial: auto-estudio o de la mano de nosotros en el Bootcamp. Suyo para siempre, auditable)</t>
   </si>
   <si>
     <t>CAO Bootcamp - Calendario Academico</t>
